--- a/output/pdf_financials_xlsx/PE.xlsx
+++ b/output/pdf_financials_xlsx/PE.xlsx
@@ -6157,16 +6157,16 @@
         <v>-0.001101</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>0.025196</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>0.042185</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.076359</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>0.077658</v>
       </c>
     </row>
     <row r="92">
@@ -6215,22 +6215,22 @@
         <v>5.429713</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.652082</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.248884</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.15396</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.910183</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.666686</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.587636</v>
       </c>
     </row>
     <row r="93">
@@ -7719,37 +7719,37 @@
         <v>0.365978</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.412962</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.344778</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-2.276228</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.010722</v>
+        <v>-2.290072</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.488449</v>
+        <v>-6.895162</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>3.916344</v>
+        <v>-2.026857</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.051394</v>
+        <v>-1.131146</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>1e-06</v>
+        <v>-0.00305</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.039551</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000421</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -10216,7 +10216,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10315,7 +10319,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11712,7 +11720,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -13773,7 +13785,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -19828,7 +19844,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PE.xlsx
+++ b/output/pdf_financials_xlsx/PE.xlsx
@@ -1037,25 +1037,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007254</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002966</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003682</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006517</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000711</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002964</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1076,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>3.9e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000264</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.273004</v>
+        <v>0.26575</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.600938</v>
+        <v>-1.603904</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.684456</v>
+        <v>-3.688138</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.344842</v>
+        <v>-1.351359</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.8461340000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.313116</v>
+        <v>-0.313827</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.360807</v>
+        <v>-3.363771</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.579167</v>
@@ -2026,16 +2026,16 @@
         <v>-0.372642</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.078324</v>
+        <v>0.07828499999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.345812</v>
+        <v>-0.346142</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.834844</v>
+        <v>-0.835108</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.251856</v>
+        <v>-0.251889</v>
       </c>
     </row>
     <row r="28">
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.273004</v>
+        <v>0.26575</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.600938</v>
+        <v>-1.603904</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.684456</v>
+        <v>-3.688138</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.344842</v>
+        <v>-1.351359</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.8461340000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.313116</v>
+        <v>-0.313827</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.360807</v>
+        <v>-3.363771</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.579167</v>
@@ -2142,16 +2142,16 @@
         <v>-0.372642</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.078324</v>
+        <v>0.07828499999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.345812</v>
+        <v>-0.346142</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.834844</v>
+        <v>-0.835108</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.251856</v>
+        <v>-0.251889</v>
       </c>
     </row>
     <row r="30">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>512.2602919653244</v>
+        <v>498.6490036401847</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -2222,16 +2222,16 @@
         <v>-145.3027579457145</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>15.46832138180827</v>
+        <v>15.46061921473444</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-64.42473391719716</v>
+        <v>-64.48621287742027</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-153.435765484286</v>
+        <v>-153.4842859768425</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-45.12157542836258</v>
+        <v>-45.12748758447217</v>
       </c>
     </row>
     <row r="31">
@@ -2410,37 +2410,37 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.741501</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.255187</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.886036</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.07253900000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.683774</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.309641</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.250772</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.371443</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.579878</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.860948</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.6203149999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2538,37 +2538,37 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.741501</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.255187</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.886036</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.07253900000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.683774</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.309641</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.250772</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.371443</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.579878</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.860948</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.6203149999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.744776</v>
+        <v>0.003275</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.258462</v>
+        <v>0.003275</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.927412</v>
+        <v>0.041376</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.119467</v>
+        <v>0.046928</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.717737</v>
+        <v>0.033963</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.320672</v>
+        <v>0.011031</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.280165</v>
+        <v>0.029393</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.373272</v>
+        <v>0.001829</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.582202</v>
+        <v>0.002324</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.884819</v>
+        <v>0.023871</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.860689</v>
+        <v>0.240374</v>
       </c>
     </row>
     <row r="49">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -46794,7 +46794,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -48911,7 +48911,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -50020,7 +50020,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E417" s="5" t="n">

--- a/output/pdf_financials_xlsx/PE.xlsx
+++ b/output/pdf_financials_xlsx/PE.xlsx
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>4.806894</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.61047</v>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
@@ -27441,7 +27441,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28568,7 +28572,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PE.xlsx
+++ b/output/pdf_financials_xlsx/PE.xlsx
@@ -792,10 +792,10 @@
         <v>0.07187200000000001</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.400867</v>
+        <v>0.489183</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.357795</v>
+        <v>0.502431</v>
       </c>
     </row>
     <row r="8">
@@ -6714,13 +6714,13 @@
         <v>-0.02597</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.333492</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020465</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.040772</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>-0.003447</v>
@@ -6729,7 +6729,7 @@
         <v>0.02922</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001516</v>
       </c>
       <c r="O101" s="3" t="n">
         <v>0</v>
@@ -7013,10 +7013,10 @@
         <v>-1.793242</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.015325</v>
+        <v>-0.03579</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.049243</v>
+        <v>-0.008470999999999999</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.282622</v>
@@ -7025,7 +7025,7 @@
         <v>0.04349</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.036769</v>
+        <v>0.035253</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>0.015266</v>
@@ -22093,7 +22093,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -24412,7 +24416,11 @@
           <t>Amounts receivable and GST/HST receivable</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -26170,7 +26178,11 @@
           <t>Amounts receivable and GST/HST receivable</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -30451,7 +30463,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
